--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487048_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487048_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.604100000000001</v>
+        <v>8.0122</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5617</v>
+        <v>6.3178</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0424</v>
+        <v>1.6944</v>
       </c>
       <c r="G2" t="n">
         <v>3.2721</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>2.56</v>
+        <v>1.9681</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6737</v>
+        <v>1.4298</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8863</v>
+        <v>0.5383</v>
       </c>
       <c r="V2" t="n">
         <v>1.228</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.5258</v>
+        <v>7.3319</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8041</v>
+        <v>8.1015</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2783</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>3.3556</v>
@@ -688,13 +688,13 @@
         <v>2.5091</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1739</v>
+        <v>0.9799</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5315</v>
+        <v>0.8289</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3576</v>
+        <v>0.151</v>
       </c>
       <c r="V3" t="n">
         <v>0.4873</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1035</v>
+        <v>3.3835</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9863</v>
+        <v>3.0254</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1171</v>
+        <v>0.3581</v>
       </c>
       <c r="G4" t="n">
         <v>0.043</v>
@@ -766,13 +766,13 @@
         <v>2.5091</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0324</v>
+        <v>1.2476</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1956</v>
+        <v>0.8435</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1632</v>
+        <v>0.4042</v>
       </c>
       <c r="V4" t="n">
         <v>1.5138</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>A. PEREZ PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0454</v>
+        <v>2.5241</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9838</v>
+        <v>0.1339</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0292</v>
+        <v>2.3902</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6757</v>
+        <v>-0.704</v>
       </c>
       <c r="H5" t="n">
-        <v>2.574</v>
+        <v>0.0414</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8983</v>
+        <v>-0.7454</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5755</v>
+        <v>-0.6847</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1617</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-1.2538</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8998</v>
+        <v>-0.0194</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5878</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3121</v>
+        <v>0.5084</v>
       </c>
       <c r="P5" t="n">
-        <v>-4.4392</v>
+        <v>1.7371</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6.7553</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3161</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8668</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>2.6242</v>
+        <v>0.2469</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2426</v>
+        <v>0.3443</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9421</v>
+        <v>0.8999</v>
       </c>
       <c r="W5" t="n">
         <v>0.5717</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3704</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. PEREZ PEREZ</t>
+          <t>J. FERRANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5574</v>
+        <v>0.6566</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8863</v>
+        <v>-0.5936</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4437</v>
+        <v>1.2501</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.704</v>
+        <v>-0.4006</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0414</v>
+        <v>-0.4006</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7454</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6847</v>
+        <v>-0.6676</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5691000000000001</v>
+        <v>-0.6676</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2538</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0194</v>
+        <v>0.267</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5276999999999999</v>
+        <v>0.267</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5084</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3755</v>
+        <v>0.2079</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7733</v>
+        <v>0.074</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3979</v>
+        <v>0.1338</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8999</v>
+        <v>0.6562</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3281</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. FERRANDEZ FERNANDEZ</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5762</v>
+        <v>0.2806</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5936</v>
+        <v>-2.2668</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1698</v>
+        <v>2.5474</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4006</v>
+        <v>1.6757</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4006</v>
+        <v>2.574</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.8983</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6676</v>
+        <v>2.5755</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6676</v>
+        <v>3.1617</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.267</v>
+        <v>-0.8998</v>
       </c>
       <c r="N7" t="n">
-        <v>0.267</v>
+        <v>-0.5878</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.3121</v>
       </c>
       <c r="P7" t="n">
-        <v>0.193</v>
+        <v>-4.4392</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-6.7553</v>
       </c>
       <c r="R7" t="n">
-        <v>0.193</v>
+        <v>2.3161</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1276</v>
+        <v>2.1019</v>
       </c>
       <c r="T7" t="n">
-        <v>0.074</v>
+        <v>1.3412</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0535</v>
+        <v>0.7608</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6562</v>
+        <v>0.9421</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5717</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6562</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1745</v>
+        <v>-0.2221</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7271</v>
+        <v>-0.6676</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5526</v>
+        <v>0.4455</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5341</v>
@@ -1078,13 +1078,13 @@
         <v>0.193</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1666</v>
+        <v>0.119</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0595</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2261</v>
+        <v>0.119</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7409</v>
+        <v>-2.7216</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1443</v>
+        <v>-3.2053</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4034</v>
+        <v>0.4837</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3693</v>
@@ -1156,13 +1156,13 @@
         <v>1.7371</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2135</v>
+        <v>0.8057</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4468</v>
+        <v>0.4921</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2333</v>
+        <v>0.3136</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.541</v>
+        <v>-3.6199</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.954</v>
+        <v>-2.4345</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.587</v>
+        <v>-1.1854</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0036</v>
@@ -1234,13 +1234,13 @@
         <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1937</v>
+        <v>0.7274</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0727</v>
+        <v>0.5923</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2664</v>
+        <v>0.1352</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5717</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0947</v>
+        <v>-6.9791</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3946</v>
+        <v>-6.9578</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2999</v>
+        <v>-0.0213</v>
       </c>
       <c r="G11" t="n">
         <v>-6.2999</v>
@@ -1312,13 +1312,13 @@
         <v>1.5441</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2355</v>
+        <v>1.3511</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3775</v>
+        <v>0.8144</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8579</v>
+        <v>0.5367</v>
       </c>
       <c r="V11" t="n">
         <v>0.2859</v>
@@ -1345,37 +1345,37 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.8613</v>
+        <v>8.6462</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3316000000000008</v>
+        <v>1.453000000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>7.192800000000001</v>
+        <v>7.193</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.965100000000001</v>
+        <v>-4.9651</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.09890000000000043</v>
+        <v>-0.09889999999999866</v>
       </c>
       <c r="I12" t="n">
         <v>-4.866200000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>4.539999999999998</v>
+        <v>4.539999999999996</v>
       </c>
       <c r="K12" t="n">
-        <v>5.7788</v>
+        <v>5.778800000000002</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.238700000000001</v>
+        <v>-1.2387</v>
       </c>
       <c r="M12" t="n">
         <v>-9.505100000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.8777</v>
+        <v>-5.877699999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-3.6274</v>
@@ -1390,13 +1390,13 @@
         <v>16.4057</v>
       </c>
       <c r="S12" t="n">
-        <v>8.315300000000001</v>
+        <v>10.0998</v>
       </c>
       <c r="T12" t="n">
-        <v>4.878400000000001</v>
+        <v>6.6631</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4368</v>
+        <v>3.4369</v>
       </c>
       <c r="V12" t="n">
         <v>5.4415</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.1045</v>
+        <v>5.6017</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9715</v>
+        <v>3.4694</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1329</v>
+        <v>2.1323</v>
       </c>
       <c r="G13" t="n">
         <v>4.752</v>
@@ -1468,13 +1468,13 @@
         <v>2.3161</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5732</v>
+        <v>0.0704</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8521</v>
+        <v>0.35</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.279</v>
+        <v>-0.2796</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5717</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.1142</v>
+        <v>2.7894</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8101</v>
+        <v>4.1105</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6959</v>
+        <v>-1.3211</v>
       </c>
       <c r="G14" t="n">
         <v>2.9063</v>
@@ -1546,13 +1546,13 @@
         <v>2.8951</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3941</v>
+        <v>-1.7189</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7456</v>
+        <v>-0.4451</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6485</v>
+        <v>-1.2738</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3281</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8115</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0633</v>
+        <v>0.1634</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7482</v>
+        <v>0.8018</v>
       </c>
       <c r="G15" t="n">
         <v>0.5234</v>
@@ -1624,13 +1624,13 @@
         <v>0.579</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2908</v>
+        <v>-0.1372</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0595</v>
+        <v>0.0407</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2313</v>
+        <v>-0.1778</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0798</v>
+        <v>0.5214</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0388</v>
+        <v>-0.8385</v>
       </c>
       <c r="F16" t="n">
-        <v>0.959</v>
+        <v>1.3599</v>
       </c>
       <c r="G16" t="n">
         <v>0.2108</v>
@@ -1702,13 +1702,13 @@
         <v>0.772</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8613</v>
+        <v>-0.2601</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5354</v>
+        <v>-0.3351</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3259</v>
+        <v>0.075</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2014</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3999</v>
+        <v>0.3084</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8697</v>
+        <v>-0.6694</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4699</v>
+        <v>0.9778</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6918</v>
@@ -1780,13 +1780,13 @@
         <v>1.9301</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5923</v>
+        <v>-0.8841</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0562</v>
+        <v>-0.856</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5361</v>
+        <v>-0.0281</v>
       </c>
       <c r="V17" t="n">
         <v>1.8842</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6844</v>
+        <v>-0.1636</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2048</v>
+        <v>-0.0045</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4796</v>
+        <v>-0.159</v>
       </c>
       <c r="G18" t="n">
         <v>3.091</v>
@@ -1858,13 +1858,13 @@
         <v>1.158</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8104</v>
+        <v>-0.2895</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6544</v>
+        <v>-0.4541</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.156</v>
+        <v>0.1646</v>
       </c>
       <c r="V18" t="n">
         <v>-1.228</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1999</v>
+        <v>-2.0928</v>
       </c>
       <c r="E19" t="n">
         <v>-1.4146</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7853</v>
+        <v>-0.6782</v>
       </c>
       <c r="G19" t="n">
         <v>-1.2613</v>
@@ -1936,13 +1936,13 @@
         <v>0.772</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7456</v>
+        <v>-0.6385</v>
       </c>
       <c r="T19" t="n">
         <v>0.1917</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9373</v>
+        <v>-0.8302</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9714</v>
+        <v>-2.8054</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0411</v>
+        <v>-1.7407</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9303</v>
+        <v>-1.0648</v>
       </c>
       <c r="G20" t="n">
         <v>1.2131</v>
@@ -2014,13 +2014,13 @@
         <v>2.8951</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.053</v>
+        <v>-0.887</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.924</v>
+        <v>-0.6236</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1289</v>
+        <v>-0.2634</v>
       </c>
       <c r="V20" t="n">
         <v>-4.0965</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8587</v>
+        <v>-3.1914</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.547</v>
+        <v>-3.7459</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6883</v>
+        <v>0.5544</v>
       </c>
       <c r="G21" t="n">
         <v>0.4552</v>
@@ -2092,13 +2092,13 @@
         <v>3.4741</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.0629</v>
+        <v>-1.3957</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5321</v>
+        <v>-0.731</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5308</v>
+        <v>-0.6647</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.6976</v>
+        <v>-7.4591</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.9219</v>
+        <v>-6.5227</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.9364</v>
       </c>
       <c r="G22" t="n">
         <v>-6.2336</v>
@@ -2170,13 +2170,13 @@
         <v>1.5441</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.078</v>
+        <v>-0.8394</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0265</v>
+        <v>-0.5744</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1045</v>
+        <v>-0.2651</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8615</v>
+        <v>-5.526200000000001</v>
       </c>
       <c r="E23" t="n">
         <v>-7.193000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3314999999999998</v>
+        <v>1.666700000000001</v>
       </c>
       <c r="G23" t="n">
         <v>4.965100000000001</v>
@@ -2248,13 +2248,13 @@
         <v>18.3356</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.315199999999999</v>
+        <v>-6.98</v>
       </c>
       <c r="T23" t="n">
         <v>-3.4369</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.8783</v>
+        <v>-3.5431</v>
       </c>
       <c r="V23" t="n">
         <v>-5.441399999999999</v>
